--- a/output/pdf_financials_xlsx/STK.xlsx
+++ b/output/pdf_financials_xlsx/STK.xlsx
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.040881</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.051287</v>
       </c>
     </row>
     <row r="93">
@@ -2938,7 +2938,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.06</v>
       </c>

--- a/output/pdf_financials_xlsx/STK.xlsx
+++ b/output/pdf_financials_xlsx/STK.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.016839</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.02692</v>
       </c>
     </row>
     <row r="13">
@@ -870,10 +870,10 @@
         <v>-0.128111</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.226836</v>
+        <v>-0.243675</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.354667</v>
+        <v>-0.381587</v>
       </c>
     </row>
     <row r="28">
@@ -902,10 +902,10 @@
         <v>-0.128111</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.226836</v>
+        <v>-0.243675</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.354667</v>
+        <v>-0.381587</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.499365</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.842064</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.540836</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.499365</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.842064</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.540836</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.499365</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.850912</v>
+        <v>0.008848</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.549712</v>
+        <v>0.008876</v>
       </c>
     </row>
     <row r="49">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">

--- a/output/pdf_financials_xlsx/STK.xlsx
+++ b/output/pdf_financials_xlsx/STK.xlsx
@@ -1528,13 +1528,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.023599</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="68">
@@ -3283,7 +3283,11 @@
           <t>Proceeds from share issue</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
